--- a/tests/fixtures/banks/kb_sample.xlsx
+++ b/tests/fixtures/banks/kb_sample.xlsx
@@ -447,54 +447,54 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>거래일자</t>
+          <t>거래일시</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>거래내역</t>
+          <t>적요</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>출금(원)</t>
+          <t>보낸분/받는분</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>입금(원)</t>
+          <t>송금메모</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>잔액(원)</t>
+          <t>출금액</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>취급점</t>
+          <t>입금액</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>보낸분/받는분</t>
+          <t>잔액</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>비고</t>
+          <t>거래점</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>거래번호</t>
+          <t>구분</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-01 01:00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -504,27 +504,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>88000</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>10000000</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>강남지점</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>KT</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -536,7 +531,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-02 02:00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -546,27 +541,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>삼성화재</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>150000</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>10000000</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>강남지점</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>삼성화재</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -578,7 +568,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2026-01-03 03:00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -588,27 +578,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>네이버</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>10000000</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>강남지점</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>네이버광고</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -620,7 +605,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-04 04:00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -630,27 +615,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+          <t>고객사</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>5000000</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>10000000</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>강남지점</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>고객사</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -662,7 +642,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-05 05:00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -670,27 +650,22 @@
           <t>???알수없음</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>10000000</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>강남지점</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>TX000005</t>
